--- a/tests/evals/timesheets/21-xlsx-elena-06/input.xlsx
+++ b/tests/evals/timesheets/21-xlsx-elena-06/input.xlsx
@@ -447,7 +447,7 @@
     <row r="5">
       <c r="A5" t="inlineStr">
         <is>
-          <t>Total: 176.00</t>
+          <t>Total: 168.00</t>
         </is>
       </c>
     </row>
